--- a/pagina/data/informe_gestantes.xlsx
+++ b/pagina/data/informe_gestantes.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Categorias'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regiones'!$A$1:$C$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Historico_mensual'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Historico_mensual'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,6 +36,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -46,9 +49,6 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <i val="1"/>
@@ -69,13 +69,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -97,22 +103,22 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -495,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Centro Emergencia Mujer y Familia · Enero - Julio 2026 (preliminar)</t>
+          <t>Centro Emergencia Mujer y Familia · Enero - Agosto 2026 (preliminar)</t>
         </is>
       </c>
     </row>
@@ -506,7 +512,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2497</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="5">
@@ -526,7 +532,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
@@ -537,7 +543,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:33</t>
+          <t>2026-09-18 09:54</t>
         </is>
       </c>
     </row>
@@ -599,10 +605,10 @@
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>1703</v>
+        <v>1971</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>68.2</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="3">
@@ -617,10 +623,10 @@
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>794</v>
+        <v>907</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>31.8</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="4">
@@ -635,10 +641,10 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>1001</v>
+        <v>1146</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>40.1</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="5">
@@ -653,10 +659,10 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>925</v>
+        <v>1067</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="6">
@@ -671,10 +677,10 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>571</v>
+        <v>665</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="7">
@@ -689,10 +695,10 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2408</v>
+        <v>2779</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -707,10 +713,10 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -725,10 +731,10 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2434</v>
+        <v>2804</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -743,10 +749,10 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -761,7 +767,7 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2496</v>
+        <v>2877</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>100</v>
@@ -797,10 +803,10 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1163</v>
+        <v>1330</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="14">
@@ -815,10 +821,10 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1112</v>
+        <v>1296</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -833,10 +839,10 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -851,10 +857,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1637</v>
+        <v>1881</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>65.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -869,10 +875,10 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>456</v>
+        <v>531</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="18">
@@ -887,7 +893,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>404</v>
+        <v>466</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>16.2</v>
@@ -905,7 +911,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>1025</v>
+        <v>1181</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>41</v>
@@ -923,10 +929,10 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>740</v>
+        <v>854</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="21">
@@ -941,7 +947,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>725</v>
+        <v>835</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>29</v>
@@ -959,7 +965,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>0.3</v>
@@ -1009,7 +1015,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>424</v>
+        <v>489</v>
       </c>
       <c r="C2" s="10" t="n">
         <v>17</v>
@@ -1022,7 +1028,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C3" s="10" t="n">
         <v>6.6</v>
@@ -1035,10 +1041,10 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1048,10 +1054,10 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6">
@@ -1061,7 +1067,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>5.1</v>
@@ -1070,11 +1076,11 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>5</v>
@@ -1083,11 +1089,11 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>4.8</v>
@@ -1100,7 +1106,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>4.8</v>
@@ -1113,20 +1119,20 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>3.9</v>
@@ -1135,11 +1141,11 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>LIMA PROVINCIA</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>3.8</v>
@@ -1152,10 +1158,10 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="14">
@@ -1165,10 +1171,10 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -1178,10 +1184,10 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -1191,10 +1197,10 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -1204,10 +1210,10 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1217,10 +1223,10 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
@@ -1230,10 +1236,10 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -1243,20 +1249,20 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>TUMBES</t>
+          <t>APURIMAC</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>1.7</v>
@@ -1265,24 +1271,24 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>APURIMAC</t>
+          <t>TUMBES</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>1.3</v>
@@ -1291,14 +1297,14 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="25">
@@ -1308,7 +1314,7 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C25" s="10" t="n">
         <v>1.2</v>
@@ -1321,7 +1327,7 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>1.1</v>
@@ -1334,7 +1340,7 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C27" s="10" t="n">
         <v>0.8</v>
@@ -1352,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1526,7 +1532,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1536,17 +1542,17 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>0 a 17 años</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>259</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1560,13 +1566,13 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>206</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1580,13 +1586,13 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>269</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1600,13 +1606,13 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1620,13 +1626,13 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -1640,31 +1646,71 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>18 a 59 años</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>18 a 59 años</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D16" s="9" t="n">
         <v>243</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>18 a 59 años</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>268</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D15"/>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>